--- a/benchmarking/evaluation_results/excel/link_prediction.xlsx
+++ b/benchmarking/evaluation_results/excel/link_prediction.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="0.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="0.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="0.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="0.1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="0.2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="0.3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.24679</v>
+        <v>0.00556</v>
       </c>
       <c r="C2" t="n">
-        <v>0.50125</v>
+        <v>0.01945</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.01514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.57741</v>
+        <v>0.0092</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5319</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.60107</v>
+        <v>0.01207</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.02414</v>
       </c>
       <c r="H2" t="n">
-        <v>0.55269</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.60893</v>
+        <v>0.00527</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01945</v>
       </c>
       <c r="J2" t="n">
-        <v>0.60768</v>
+        <v>0.01763</v>
       </c>
     </row>
     <row r="3">
@@ -520,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5926399999999999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.60692</v>
+        <v>0.03401</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.03516</v>
       </c>
       <c r="D3" t="n">
-        <v>0.61094</v>
+        <v>0.02175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.60864</v>
+        <v>0.01552</v>
       </c>
       <c r="F3" t="n">
-        <v>0.60634</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.6141</v>
+        <v>0.01964</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03257</v>
       </c>
       <c r="H3" t="n">
-        <v>0.59801</v>
+        <v>0.0068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6125699999999999</v>
+        <v>0.02577</v>
       </c>
       <c r="J3" t="n">
-        <v>0.61046</v>
+        <v>0.02213</v>
       </c>
     </row>
     <row r="4">
@@ -553,32 +554,32 @@
           <t>hits_at_5</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.61046</v>
+      <c r="B4" s="2" t="n">
+        <v>0.04551</v>
       </c>
       <c r="C4" t="n">
-        <v>0.61228</v>
+        <v>0.03918</v>
       </c>
       <c r="D4" t="n">
-        <v>0.61142</v>
+        <v>0.0228</v>
       </c>
       <c r="E4" t="n">
-        <v>0.60998</v>
+        <v>0.01724</v>
       </c>
       <c r="F4" t="n">
-        <v>0.61075</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.61535</v>
+        <v>0.02328</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03497</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6017400000000001</v>
+        <v>0.00738</v>
       </c>
       <c r="I4" t="n">
-        <v>0.61314</v>
+        <v>0.02826</v>
       </c>
       <c r="J4" t="n">
-        <v>0.61084</v>
+        <v>0.02309</v>
       </c>
     </row>
     <row r="5">
@@ -588,31 +589,31 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.61678</v>
+        <v>0.04905</v>
       </c>
       <c r="C5" t="n">
-        <v>0.61583</v>
+        <v>0.04225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.61161</v>
+        <v>0.02433</v>
       </c>
       <c r="E5" t="n">
-        <v>0.61075</v>
+        <v>0.01926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6119</v>
+        <v>0.02577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.61592</v>
+        <v>0.03708</v>
       </c>
       <c r="H5" t="n">
-        <v>0.60471</v>
+        <v>0.007860000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.61324</v>
+        <v>0.02941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.61094</v>
+        <v>0.02405</v>
       </c>
     </row>
     <row r="6">
@@ -622,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7270.63574</v>
+        <v>17821.70508</v>
       </c>
       <c r="C6" t="n">
-        <v>7010.11865</v>
+        <v>17597.23242</v>
       </c>
       <c r="D6" t="n">
-        <v>9415.219730000001</v>
+        <v>16212.12988</v>
       </c>
       <c r="E6" t="n">
-        <v>7307.97852</v>
+        <v>18019.55078</v>
       </c>
       <c r="F6" t="n">
-        <v>8844.747069999999</v>
+        <v>17243.3418</v>
       </c>
       <c r="G6" t="n">
-        <v>7308.16113</v>
+        <v>17791.36523</v>
       </c>
       <c r="H6" t="n">
-        <v>7272.8208</v>
+        <v>18102.74805</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9686.122069999999</v>
+        <v>23723.10352</v>
       </c>
       <c r="J6" t="n">
-        <v>7958.69531</v>
+        <v>18652.7207</v>
       </c>
     </row>
     <row r="7">
@@ -656,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.41976</v>
+        <v>0.02141</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5531700000000001</v>
+        <v>0.02853</v>
       </c>
       <c r="D7" t="n">
-        <v>0.60931</v>
+        <v>0.01889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.59277</v>
+        <v>0.01317</v>
       </c>
       <c r="F7" t="n">
-        <v>0.56909</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6078</v>
+        <v>0.01683</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.02921</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5754899999999999</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0.61082</v>
+        <v>0.00649</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.02323</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6091</v>
+        <v>0.02037</v>
       </c>
     </row>
     <row r="8">
@@ -690,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.39251</v>
+        <v>0.96213</v>
       </c>
       <c r="C8" t="n">
-        <v>0.37845</v>
+        <v>0.95001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.50829</v>
+        <v>0.87523</v>
       </c>
       <c r="E8" t="n">
-        <v>0.39453</v>
+        <v>0.97281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.47749</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.39454</v>
+        <v>0.96049</v>
       </c>
       <c r="H8" t="n">
-        <v>0.39263</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.5229200000000001</v>
+        <v>1.28072</v>
       </c>
       <c r="J8" t="n">
-        <v>0.42966</v>
+        <v>1.00699</v>
       </c>
     </row>
     <row r="9">
@@ -724,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.41958</v>
+        <v>0.02112</v>
       </c>
       <c r="C9" t="n">
-        <v>0.55303</v>
+        <v>0.02823</v>
       </c>
       <c r="D9" t="n">
-        <v>0.60919</v>
+        <v>0.0186</v>
       </c>
       <c r="E9" t="n">
-        <v>0.59265</v>
+        <v>0.01288</v>
       </c>
       <c r="F9" t="n">
-        <v>0.56896</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.60768</v>
+        <v>0.01653</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.02892</v>
       </c>
       <c r="H9" t="n">
-        <v>0.57537</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.6107</v>
+        <v>0.00619</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02294</v>
       </c>
       <c r="J9" t="n">
-        <v>0.60899</v>
+        <v>0.02008</v>
       </c>
     </row>
   </sheetData>
@@ -819,31 +820,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00556</v>
+        <v>0.24679</v>
       </c>
       <c r="C2" t="n">
-        <v>0.49186</v>
+        <v>0.50125</v>
       </c>
       <c r="D2" t="n">
-        <v>0.55106</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5073800000000001</v>
+        <v>0.57741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.47854</v>
+        <v>0.5319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.53593</v>
+        <v>0.60107</v>
       </c>
       <c r="H2" t="n">
-        <v>0.42958</v>
+        <v>0.55269</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.55365</v>
+        <v>0.60893</v>
       </c>
       <c r="J2" t="n">
-        <v>0.54867</v>
+        <v>0.60768</v>
       </c>
     </row>
     <row r="3">
@@ -853,31 +854,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.54493</v>
+        <v>0.5926399999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.55375</v>
+        <v>0.60692</v>
       </c>
       <c r="D3" t="n">
-        <v>0.55528</v>
+        <v>0.61094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.54349</v>
+        <v>0.60864</v>
       </c>
       <c r="F3" t="n">
-        <v>0.55154</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.55537</v>
+        <v>0.60634</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.6141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.48304</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.59801</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.6125699999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.55375</v>
+        <v>0.61046</v>
       </c>
     </row>
     <row r="4">
@@ -887,31 +888,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.55748</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.55787</v>
+        <v>0.61046</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.61228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.55566</v>
+        <v>0.61142</v>
       </c>
       <c r="E4" t="n">
-        <v>0.54848</v>
+        <v>0.60998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5548999999999999</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.5571</v>
+        <v>0.61075</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.61535</v>
       </c>
       <c r="H4" t="n">
-        <v>0.49732</v>
+        <v>0.6017400000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.55719</v>
+        <v>0.61314</v>
       </c>
       <c r="J4" t="n">
-        <v>0.55403</v>
+        <v>0.61084</v>
       </c>
     </row>
     <row r="5">
@@ -921,31 +922,31 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.56064</v>
+        <v>0.61678</v>
       </c>
       <c r="C5" t="n">
-        <v>0.55902</v>
+        <v>0.61583</v>
       </c>
       <c r="D5" t="n">
-        <v>0.55585</v>
+        <v>0.61161</v>
       </c>
       <c r="E5" t="n">
-        <v>0.55355</v>
+        <v>0.61075</v>
       </c>
       <c r="F5" t="n">
-        <v>0.55614</v>
+        <v>0.6119</v>
       </c>
       <c r="G5" t="n">
-        <v>0.55825</v>
+        <v>0.61592</v>
       </c>
       <c r="H5" t="n">
-        <v>0.51523</v>
+        <v>0.60471</v>
       </c>
       <c r="I5" t="n">
-        <v>0.55729</v>
+        <v>0.61324</v>
       </c>
       <c r="J5" t="n">
-        <v>0.55422</v>
+        <v>0.61094</v>
       </c>
     </row>
     <row r="6">
@@ -955,31 +956,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8040.78174</v>
+        <v>7270.63574</v>
       </c>
       <c r="C6" t="n">
-        <v>8313.999019999999</v>
+        <v>7010.11865</v>
       </c>
       <c r="D6" t="n">
-        <v>8349.26953</v>
+        <v>9415.219730000001</v>
       </c>
       <c r="E6" t="n">
-        <v>8070.33154</v>
+        <v>7307.97852</v>
       </c>
       <c r="F6" t="n">
-        <v>7674.76074</v>
+        <v>8844.747069999999</v>
       </c>
       <c r="G6" t="n">
-        <v>8075.26709</v>
+        <v>7308.16113</v>
       </c>
       <c r="H6" t="n">
-        <v>8268.360350000001</v>
+        <v>7272.8208</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10561.12109</v>
+        <v>9686.122069999999</v>
       </c>
       <c r="J6" t="n">
-        <v>8225.86328</v>
+        <v>7958.69531</v>
       </c>
     </row>
     <row r="7">
@@ -989,31 +990,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.27012</v>
+        <v>0.41976</v>
       </c>
       <c r="C7" t="n">
-        <v>0.52218</v>
+        <v>0.5531700000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.55322</v>
+        <v>0.60931</v>
       </c>
       <c r="E7" t="n">
-        <v>0.52608</v>
+        <v>0.59277</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5148</v>
+        <v>0.56909</v>
       </c>
       <c r="G7" t="n">
-        <v>0.54574</v>
+        <v>0.6078</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4613</v>
+        <v>0.5754899999999999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.55535</v>
+        <v>0.61082</v>
       </c>
       <c r="J7" t="n">
-        <v>0.55125</v>
+        <v>0.6091</v>
       </c>
     </row>
     <row r="8">
@@ -1023,31 +1024,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.43409</v>
+        <v>0.39251</v>
       </c>
       <c r="C8" t="n">
-        <v>0.44884</v>
+        <v>0.37845</v>
       </c>
       <c r="D8" t="n">
-        <v>0.45074</v>
+        <v>0.50829</v>
       </c>
       <c r="E8" t="n">
-        <v>0.43569</v>
+        <v>0.39453</v>
       </c>
       <c r="F8" t="n">
-        <v>0.41433</v>
+        <v>0.47749</v>
       </c>
       <c r="G8" t="n">
-        <v>0.43595</v>
+        <v>0.39454</v>
       </c>
       <c r="H8" t="n">
-        <v>0.44638</v>
+        <v>0.39263</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.57015</v>
+        <v>0.5229200000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.44408</v>
+        <v>0.42966</v>
       </c>
     </row>
     <row r="9">
@@ -1057,31 +1058,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2699</v>
+        <v>0.41958</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5220399999999999</v>
+        <v>0.55303</v>
       </c>
       <c r="D9" t="n">
-        <v>0.55309</v>
+        <v>0.60919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.52594</v>
+        <v>0.59265</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5146500000000001</v>
+        <v>0.56896</v>
       </c>
       <c r="G9" t="n">
-        <v>0.54561</v>
+        <v>0.60768</v>
       </c>
       <c r="H9" t="n">
-        <v>0.46114</v>
+        <v>0.57537</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.55522</v>
+        <v>0.6107</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5511200000000001</v>
+        <v>0.60899</v>
       </c>
     </row>
   </sheetData>
@@ -1152,31 +1153,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02932</v>
+        <v>0.00556</v>
       </c>
       <c r="C2" t="n">
-        <v>0.44108</v>
+        <v>0.49186</v>
       </c>
       <c r="D2" t="n">
-        <v>0.47385</v>
+        <v>0.55106</v>
       </c>
       <c r="E2" t="n">
-        <v>0.44807</v>
+        <v>0.5073800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.41176</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.48371</v>
+        <v>0.47854</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.53593</v>
       </c>
       <c r="H2" t="n">
-        <v>0.40554</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.48199</v>
+        <v>0.42958</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.55365</v>
       </c>
       <c r="J2" t="n">
-        <v>0.47662</v>
+        <v>0.54867</v>
       </c>
     </row>
     <row r="3">
@@ -1186,31 +1187,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.45919</v>
+        <v>0.54493</v>
       </c>
       <c r="C3" t="n">
-        <v>0.48103</v>
+        <v>0.55375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.48237</v>
+        <v>0.55528</v>
       </c>
       <c r="E3" t="n">
-        <v>0.475</v>
+        <v>0.54349</v>
       </c>
       <c r="F3" t="n">
-        <v>0.48046</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.48534</v>
+        <v>0.55154</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.55537</v>
       </c>
       <c r="H3" t="n">
-        <v>0.45219</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.484</v>
+        <v>0.48304</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.5570000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.47969</v>
+        <v>0.55375</v>
       </c>
     </row>
     <row r="4">
@@ -1220,31 +1221,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.48017</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.48295</v>
+        <v>0.55748</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.55787</v>
       </c>
       <c r="D4" t="n">
-        <v>0.48304</v>
+        <v>0.55566</v>
       </c>
       <c r="E4" t="n">
-        <v>0.47797</v>
+        <v>0.54848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.48323</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.48582</v>
+        <v>0.5548999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5571</v>
       </c>
       <c r="H4" t="n">
-        <v>0.46149</v>
+        <v>0.49732</v>
       </c>
       <c r="I4" t="n">
-        <v>0.48419</v>
+        <v>0.55719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.48036</v>
+        <v>0.55403</v>
       </c>
     </row>
     <row r="5">
@@ -1254,31 +1255,31 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.48716</v>
+        <v>0.56064</v>
       </c>
       <c r="C5" t="n">
-        <v>0.48352</v>
+        <v>0.55902</v>
       </c>
       <c r="D5" t="n">
-        <v>0.48323</v>
+        <v>0.55585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.47998</v>
+        <v>0.55355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4839</v>
+        <v>0.55614</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4862</v>
+        <v>0.55825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.46992</v>
+        <v>0.51523</v>
       </c>
       <c r="I5" t="n">
-        <v>0.48448</v>
+        <v>0.55729</v>
       </c>
       <c r="J5" t="n">
-        <v>0.48065</v>
+        <v>0.55422</v>
       </c>
     </row>
     <row r="6">
@@ -1288,31 +1289,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9105.5332</v>
+        <v>8040.78174</v>
       </c>
       <c r="C6" t="n">
-        <v>8961.549800000001</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>12475.57812</v>
+        <v>8313.999019999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8349.26953</v>
       </c>
       <c r="E6" t="n">
-        <v>9471.273440000001</v>
+        <v>8070.33154</v>
       </c>
       <c r="F6" t="n">
-        <v>8521.556640000001</v>
+        <v>7674.76074</v>
       </c>
       <c r="G6" t="n">
-        <v>9123.30176</v>
+        <v>8075.26709</v>
       </c>
       <c r="H6" t="n">
-        <v>9568.15137</v>
-      </c>
-      <c r="I6" t="n">
-        <v>12431.0332</v>
+        <v>8268.360350000001</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>10561.12109</v>
       </c>
       <c r="J6" t="n">
-        <v>9580.472659999999</v>
+        <v>8225.86328</v>
       </c>
     </row>
     <row r="7">
@@ -1322,31 +1323,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.24264</v>
+        <v>0.27012</v>
       </c>
       <c r="C7" t="n">
-        <v>0.46083</v>
+        <v>0.52218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.47821</v>
+        <v>0.55322</v>
       </c>
       <c r="E7" t="n">
-        <v>0.46211</v>
+        <v>0.52608</v>
       </c>
       <c r="F7" t="n">
-        <v>0.44566</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.48473</v>
+        <v>0.5148</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.54574</v>
       </c>
       <c r="H7" t="n">
-        <v>0.43107</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.48308</v>
+        <v>0.4613</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.55535</v>
       </c>
       <c r="J7" t="n">
-        <v>0.47844</v>
+        <v>0.55125</v>
       </c>
     </row>
     <row r="8">
@@ -1356,31 +1357,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.49157</v>
+        <v>0.43409</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4838</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.6735100000000001</v>
+        <v>0.44884</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.45074</v>
       </c>
       <c r="E8" t="n">
-        <v>0.51132</v>
+        <v>0.43569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.46004</v>
+        <v>0.41433</v>
       </c>
       <c r="G8" t="n">
-        <v>0.49253</v>
+        <v>0.43595</v>
       </c>
       <c r="H8" t="n">
-        <v>0.51655</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.6711</v>
+        <v>0.44638</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.57015</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5172099999999999</v>
+        <v>0.44408</v>
       </c>
     </row>
     <row r="9">
@@ -1390,31 +1391,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.24242</v>
+        <v>0.2699</v>
       </c>
       <c r="C9" t="n">
-        <v>0.46067</v>
+        <v>0.5220399999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.47805</v>
+        <v>0.55309</v>
       </c>
       <c r="E9" t="n">
-        <v>0.46195</v>
+        <v>0.52594</v>
       </c>
       <c r="F9" t="n">
-        <v>0.44549</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.48458</v>
+        <v>0.5146500000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.54561</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4309</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.48292</v>
+        <v>0.46114</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.55522</v>
       </c>
       <c r="J9" t="n">
-        <v>0.47828</v>
+        <v>0.5511200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1485,6 +1486,339 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.02932</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.48371</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.48199</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.47662</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hits_at_3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.45919</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.48103</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.48237</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.48534</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.47969</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>hits_at_5</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.48295</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.48304</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.47797</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.48323</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.48582</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.46149</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.48036</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hits_at_10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.48352</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.48323</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.47998</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4862</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.46992</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.48065</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>mr</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9105.5332</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8961.549800000001</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>12475.57812</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9471.273440000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8521.556640000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9123.30176</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9568.15137</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12431.0332</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9580.472659999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mrr</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.24264</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.47821</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.44566</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.43107</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.48308</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.47844</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_mr</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.49157</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.6735100000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.51132</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.46004</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.51655</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6711</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5172099999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_mrr</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.24242</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.48458</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.48292</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.47828</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>TransE</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DistMult</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ComplEx</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>HolE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ConvE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PairRE</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AutoSF</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BoxE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>RotatE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>hits_at_1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.00431</v>
       </c>
       <c r="C2" t="n">
